--- a/business_surveys/045_outline_creation_survey--business_surveys.xlsx
+++ b/business_surveys/045_outline_creation_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'general_business'}</t>
+          <t>general_business</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'General Business'}</t>
+          <t>General Business</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'hierarchical'}</t>
+          <t>hierarchical</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Hierarchical'}</t>
+          <t>Hierarchical</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'linear'}</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Linear'}</t>
+          <t>Linear</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'paragraphs'}</t>
+          <t>paragraphs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Paragraphs'}</t>
+          <t>Paragraphs</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'headings'}</t>
+          <t>headings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Headings'}</t>
+          <t>Headings</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'images'}</t>
+          <t>images</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Images'}</t>
+          <t>Images</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'alphabetical'}</t>
+          <t>alphabetical</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Alphabetical'}</t>
+          <t>Alphabetical</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'random'}</t>
+          <t>random</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Random'}</t>
+          <t>Random</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'sequential'}</t>
+          <t>sequential</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Sequential'}</t>
+          <t>Sequential</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'left'}</t>
+          <t>left</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Left'}</t>
+          <t>Left</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'right'}</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Right'}</t>
+          <t>Right</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'center'}</t>
+          <t>center</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Center'}</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'published'}</t>
+          <t>published</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Published'}</t>
+          <t>Published</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
